--- a/e2e/downloadedFile/sub_Transfer.xlsx
+++ b/e2e/downloadedFile/sub_Transfer.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="47">
   <si>
     <t>DAFTAR PEMBAYARAN GAJI KARYAWAN</t>
   </si>
@@ -47,256 +47,103 @@
     <t>TOTAL TRANSFER (USD)</t>
   </si>
   <si>
-    <t>Citra</t>
+    <t>ADROALDINO DA SILVA NORONHA TOME</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>Customer Service Staff Manufahi</t>
+  </si>
+  <si>
+    <t>$ 502.00</t>
+  </si>
+  <si>
+    <t>$ 0.00</t>
+  </si>
+  <si>
+    <t>AGOSTINHO GOMES FERNANDES</t>
   </si>
   <si>
     <t>Expat</t>
   </si>
   <si>
-    <t>Human Capital Manager</t>
-  </si>
-  <si>
-    <t>$ 163.92</t>
-  </si>
-  <si>
-    <t>$ 5.60</t>
-  </si>
-  <si>
-    <t>$ 158.32</t>
-  </si>
-  <si>
-    <t>dominika</t>
+    <t>Customer Service Staff Ermera</t>
+  </si>
+  <si>
+    <t>$ 503.00</t>
+  </si>
+  <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>Human Capital Operational Assistant Manager</t>
+  </si>
+  <si>
+    <t>CLAUDIO DA COSTA ALVES</t>
+  </si>
+  <si>
+    <t>Service Solution Support Officer</t>
+  </si>
+  <si>
+    <t>DIAN EVIYANTI APLUGI</t>
   </si>
   <si>
     <t>Customer Care Manager (PJ)</t>
   </si>
   <si>
-    <t>$ 111.24</t>
-  </si>
-  <si>
-    <t>$ 3.60</t>
-  </si>
-  <si>
-    <t>$ 107.64</t>
-  </si>
-  <si>
-    <t>Santos</t>
-  </si>
-  <si>
-    <t>Local</t>
-  </si>
-  <si>
-    <t>Asset Management Support Officer</t>
-  </si>
-  <si>
-    <t>$ 231.24</t>
-  </si>
-  <si>
-    <t>$ 227.64</t>
-  </si>
-  <si>
-    <t>HELENA</t>
+    <t>AHMAD RIYANA SAPUTRA</t>
+  </si>
+  <si>
+    <t>Enterprise &amp; Wholesale Sales Solution Assistant Manager</t>
+  </si>
+  <si>
+    <t>FRIESCA AMELIA</t>
+  </si>
+  <si>
+    <t>Business Planning &amp; Performance Senior Manager</t>
+  </si>
+  <si>
+    <t>HERU YULIANTO</t>
+  </si>
+  <si>
+    <t>VP Marketing &amp; Sales</t>
+  </si>
+  <si>
+    <t>RIMBUN SIBURIAN</t>
+  </si>
+  <si>
+    <t>Quality Assuance Senior Engineer</t>
+  </si>
+  <si>
+    <t>$ 402.42</t>
+  </si>
+  <si>
+    <t>SYALDY KHARISMA ANANDA</t>
+  </si>
+  <si>
+    <t>O&amp;M Network Senior Manager</t>
+  </si>
+  <si>
+    <t>Lestari Putri Cantika</t>
   </si>
   <si>
     <t>Homestaff</t>
   </si>
   <si>
-    <t>VP Mobile Network Operation (MNO)</t>
-  </si>
-  <si>
-    <t>$ 168.28</t>
-  </si>
-  <si>
-    <t>$ 62.75</t>
-  </si>
-  <si>
-    <t>$ 105.53</t>
-  </si>
-  <si>
-    <t>DEDY EDWARD AMBARITA</t>
-  </si>
-  <si>
-    <t>VP Finance Business Partner</t>
-  </si>
-  <si>
-    <t>$ 600.00</t>
-  </si>
-  <si>
-    <t>$ 0.00</t>
-  </si>
-  <si>
-    <t>ADRIANTO LEBRE</t>
-  </si>
-  <si>
-    <t>CME, RAN, Transport Planning &amp; Deployment Assistant Manager</t>
-  </si>
-  <si>
-    <t>$ 230.00</t>
-  </si>
-  <si>
-    <t>$ 7.73</t>
-  </si>
-  <si>
-    <t>$ 222.27</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>Municipio Coordinator Manatuto</t>
-  </si>
-  <si>
-    <t>$ 225.21</t>
-  </si>
-  <si>
-    <t>$ 2.40</t>
-  </si>
-  <si>
-    <t>$ 222.81</t>
-  </si>
-  <si>
-    <t>AHMAD RIYANA SAPUTRA</t>
-  </si>
-  <si>
-    <t>Enterprise &amp; Wholesale Sales Solution Assistant Manager</t>
-  </si>
-  <si>
-    <t>$ 276.13</t>
-  </si>
-  <si>
-    <t>0000002</t>
-  </si>
-  <si>
-    <t>Syifa Hadju</t>
-  </si>
-  <si>
-    <t>Accounting Support Officer</t>
-  </si>
-  <si>
-    <t>$ 63.03</t>
-  </si>
-  <si>
-    <t>$ 28.17</t>
-  </si>
-  <si>
-    <t>$ 34.86</t>
-  </si>
-  <si>
-    <t>ALCINO DE FATIMA M. VALENTE</t>
-  </si>
-  <si>
-    <t>Fiber Optic Expert</t>
-  </si>
-  <si>
-    <t>$ 100.00</t>
-  </si>
-  <si>
-    <t>CELIA MARIA REGO DE FATIMA</t>
-  </si>
-  <si>
-    <t>Human Capital Operational Assistant Manager</t>
-  </si>
-  <si>
-    <t>$ 358.00</t>
-  </si>
-  <si>
-    <t>$ 14.80</t>
-  </si>
-  <si>
-    <t>$ 343.20</t>
-  </si>
-  <si>
-    <t>ADROALDINO DA SILVA NORONHA TOME</t>
-  </si>
-  <si>
-    <t>Outsource</t>
-  </si>
-  <si>
-    <t>Customer Service Staff Manufahi</t>
-  </si>
-  <si>
-    <t>$ 180.00</t>
-  </si>
-  <si>
-    <t>$ 7.20</t>
-  </si>
-  <si>
-    <t>$ 172.80</t>
-  </si>
-  <si>
-    <t>DIAN EVIYANTI APLUGI</t>
-  </si>
-  <si>
-    <t>$ 300.00</t>
-  </si>
-  <si>
-    <t>FRIESCA AMELIA</t>
-  </si>
-  <si>
-    <t>Business Planning &amp; Performance Senior Manager</t>
-  </si>
-  <si>
-    <t>$ 700.00</t>
-  </si>
-  <si>
-    <t>$ 44.75</t>
-  </si>
-  <si>
-    <t>$ 655.25</t>
-  </si>
-  <si>
-    <t>HERU YULIANTO</t>
-  </si>
-  <si>
-    <t>VP Marketing &amp; Sales</t>
-  </si>
-  <si>
-    <t>SYALDY KHARISMA ANANDA</t>
-  </si>
-  <si>
-    <t>O&amp;M Network Senior Manager</t>
-  </si>
-  <si>
-    <t>RIMBUN SIBURIAN</t>
-  </si>
-  <si>
-    <t>Quality Assuance Senior Engineer</t>
-  </si>
-  <si>
-    <t>$ 527.00</t>
-  </si>
-  <si>
-    <t>Lestari Putri Cantika</t>
-  </si>
-  <si>
     <t>Marketing &amp; Retail Senior Manager</t>
   </si>
   <si>
     <t>$ 504.00</t>
   </si>
   <si>
-    <t>AGOSTINHO GOMES FERNANDES</t>
-  </si>
-  <si>
-    <t>Customer Service Staff Ermera</t>
-  </si>
-  <si>
-    <t>$ 511.00</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>$ 6,249.05</t>
-  </si>
-  <si>
-    <t>$ 180.60</t>
-  </si>
-  <si>
-    <t>$ 6,068.45</t>
-  </si>
-  <si>
-    <t>DILI, 14 August 2026</t>
+    <t>$ 5,425.42</t>
+  </si>
+  <si>
+    <t>DILI, 18 August 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
@@ -394,7 +241,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="514350" cy="333375"/>
@@ -713,14 +560,14 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="true" style="0"/>
-    <col min="2" max="2" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="38.848" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="70.697" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="65.984" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="12.854" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="19.995" bestFit="true" customWidth="true" style="0"/>
     <col min="8" max="8" width="24.708" bestFit="true" customWidth="true" style="0"/>
@@ -770,7 +617,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>900145</v>
+        <v>24016</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
@@ -788,7 +635,7 @@
         <v>14</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -796,13 +643,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2">
-        <v>83005</v>
+        <v>26013</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>17</v>
@@ -811,10 +658,10 @@
         <v>18</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -822,25 +669,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="2">
-        <v>85014</v>
+        <v>92003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -848,25 +695,25 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>84016</v>
+        <v>24005</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -874,25 +721,25 @@
         <v>5</v>
       </c>
       <c r="B9" s="2">
-        <v>85006</v>
+        <v>79001</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -900,25 +747,25 @@
         <v>6</v>
       </c>
       <c r="B10" s="2">
-        <v>88015</v>
+        <v>95008</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -926,25 +773,25 @@
         <v>7</v>
       </c>
       <c r="B11" s="2">
-        <v>83008</v>
+        <v>91009</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -952,51 +799,51 @@
         <v>8</v>
       </c>
       <c r="B12" s="2">
-        <v>95008</v>
+        <v>74003</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2">
         <v>9</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>49</v>
+      <c r="B13" s="2">
+        <v>81010</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1004,25 +851,25 @@
         <v>10</v>
       </c>
       <c r="B14" s="2">
-        <v>26014</v>
+        <v>91015</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1030,293 +877,85 @@
         <v>11</v>
       </c>
       <c r="B15" s="2">
-        <v>92003</v>
+        <v>999999</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="2">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2">
-        <v>24016</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>68</v>
+      <c r="A16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="2">
-        <v>13</v>
-      </c>
-      <c r="B17" s="2">
-        <v>79001</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>70</v>
-      </c>
+      <c r="A17"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="2">
-        <v>14</v>
-      </c>
-      <c r="B18" s="2">
-        <v>91009</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>75</v>
-      </c>
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18"/>
+      <c r="F18"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="2">
-        <v>15</v>
-      </c>
-      <c r="B19" s="2">
-        <v>74003</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="2">
-        <v>16</v>
-      </c>
-      <c r="B20" s="2">
-        <v>91015</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>70</v>
-      </c>
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19"/>
+      <c r="F19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" customHeight="1" ht="37.5">
+      <c r="A20"/>
+      <c r="E20"/>
+      <c r="F20"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="2">
-        <v>17</v>
-      </c>
-      <c r="B21" s="2">
-        <v>81010</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>82</v>
+      <c r="A21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21"/>
+      <c r="F21" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="2">
-        <v>18</v>
-      </c>
-      <c r="B22" s="2">
-        <v>999999</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="2">
-        <v>19</v>
-      </c>
-      <c r="B23" s="2">
-        <v>26013</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>93</v>
-      </c>
-      <c r="E26"/>
-      <c r="F26"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" t="s">
-        <v>94</v>
-      </c>
-      <c r="E27"/>
-      <c r="F27" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" customHeight="1" ht="37.5">
-      <c r="A28"/>
-      <c r="E28"/>
-      <c r="F28"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E29"/>
-      <c r="F29" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" t="s">
-        <v>96</v>
-      </c>
-      <c r="E30"/>
-      <c r="F30" t="s">
-        <v>97</v>
+      <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22"/>
+      <c r="F22" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1324,23 +963,23 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="E26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="E27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="E28:E28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="E29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="E30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="E19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="E20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="E22:E22"/>
+    <mergeCell ref="F22:H22"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
